--- a/frontend/public/originals/mnt-equipment-list.xlsx
+++ b/frontend/public/originals/mnt-equipment-list.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3C41CEC-AA98-4F6D-9A9E-03AFE018DDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C254A07A-BDF6-416F-A64E-83163634D565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3506,6 +3506,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0" top="0.19685039370078741" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="65" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>